--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -851,32 +851,32 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>PH-01</t>
+          <t>SP-08</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Phòng</t>
+          <t>Sản phẩm</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Thêm phòng mới</t>
+          <t>Đổi giá hàng loạt nhiều sản phẩm</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Admin điền form và lưu phòng mới</t>
+          <t>Admin chọn nhiều sản phẩm cùng lúc rồi nhập một giá mới, áp dụng cho tất cả</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Phòng xuất hiện trong danh sách quản lý phòng</t>
+          <t>Tất cả sản phẩm được chọn đổi thành đúng giá mới, sản phẩm không được chọn giữ nguyên giá cũ</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5 -&gt; 6</t>
+          <t>A=18000.0 B=18000.0 untouched=33333.0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -901,32 +901,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>PH-02</t>
+          <t>SP-09</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Phòng</t>
+          <t>Sản phẩm</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sửa phòng</t>
+          <t>Xóa hàng loạt nhiều sản phẩm</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Admin đổi tên, giá, sức chứa của một phòng có sẵn</t>
+          <t>Admin chọn nhiều sản phẩm (một sản phẩm chưa từng bán, một sản phẩm đã có đơn hàng) rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Thông tin phòng được cập nhật đúng như đã sửa</t>
+          <t>Sản phẩm chưa từng bán bị xóa hẳn; sản phẩm đã có đơn hàng chỉ bị ẩn - giống hệt quy tắc xóa từng cái một</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -934,10 +934,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>A đã xóa hẳn=True, B đã có đơn nên chỉ ẩn=True</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -947,7 +951,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PH-03</t>
+          <t>PH-01</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -957,22 +961,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Bật/tắt trạng thái phòng trống</t>
+          <t>Thêm phòng mới</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Admin bấm nút đổi trạng thái mở/đóng phòng</t>
+          <t>Admin điền form và lưu phòng mới</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái available đảo ngược đúng</t>
+          <t>Phòng xuất hiện trong danh sách quản lý phòng</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -980,10 +984,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5 -&gt; 6</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -993,7 +1001,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PH-04</t>
+          <t>PH-02</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1003,22 +1011,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Xóa phòng chưa từng có lịch đặt</t>
+          <t>Sửa phòng</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Admin xóa một phòng chưa từng được đặt</t>
+          <t>Admin đổi tên, giá, sức chứa của một phòng có sẵn</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Phòng bị xóa hẳn khỏi cơ sở dữ liệu</t>
+          <t>Thông tin phòng được cập nhật đúng như đã sửa</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1029,7 +1037,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1047,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PH-05</t>
+          <t>PH-03</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1049,22 +1057,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Xóa phòng đã có lịch đặt</t>
+          <t>Bật/tắt trạng thái phòng trống</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Admin xóa một phòng đã từng có người đặt (RoomBooking)</t>
+          <t>Admin bấm nút đổi trạng thái mở/đóng phòng</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Không xóa hẳn (vì phá vỡ lịch sử đặt phòng) - tự động đóng phòng, lịch sử vẫn giữ nguyên</t>
+          <t>Trạng thái available đảo ngược đúng</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1072,14 +1080,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>phòng vẫn còn nhưng available=False</t>
-        </is>
-      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PH-06</t>
+          <t>PH-04</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1099,22 +1103,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật trạng thái đặt phòng</t>
+          <t>Xóa phòng chưa từng có lịch đặt</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Admin đổi trạng thái một lượt đặt phòng (chờ/xác nhận/hủy)</t>
+          <t>Admin xóa một phòng chưa từng được đặt</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đặt phòng được cập nhật đúng</t>
+          <t>Phòng bị xóa hẳn khỏi cơ sở dữ liệu</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1125,7 +1129,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1135,32 +1139,32 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>PH-05</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng</t>
+          <t>Phòng</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tạo đơn tại quầy (POS)</t>
+          <t>Xóa phòng đã có lịch đặt</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Admin chọn món và tạo đơn ngay tại quầy bán hàng</t>
+          <t>Admin xóa một phòng đã từng có người đặt (RoomBooking)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng mới được tạo, tồn kho sản phẩm bị trừ đúng số lượng</t>
+          <t>Không xóa hẳn (vì phá vỡ lịch sử đặt phòng) - tự động đóng phòng, lịch sử vẫn giữ nguyên</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1170,12 +1174,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>đơn 5-&gt;6, tồn kho 47-&gt;46</t>
+          <t>phòng vẫn còn nhưng available=False</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1185,17 +1189,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>DH-02</t>
+          <t>PH-06</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng</t>
+          <t>Phòng</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật trạng thái đơn hàng</t>
+          <t>Cập nhật trạng thái đặt phòng</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1205,12 +1209,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Admin đổi trạng thái đơn từ "còn nợ" sang "hoàn thành"</t>
+          <t>Admin đổi trạng thái một lượt đặt phòng (chờ/xác nhận/hủy)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đơn hàng được cập nhật đúng</t>
+          <t>Trạng thái đặt phòng được cập nhật đúng</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1221,7 +1225,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1231,32 +1235,32 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>DH-03</t>
+          <t>PH-07</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng</t>
+          <t>Phòng</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Xóa đơn hàng - Super Admin</t>
+          <t>Đổi giá hàng loạt nhiều phòng</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Super Admin xóa một đơn hàng test</t>
+          <t>Admin chọn nhiều phòng cùng lúc rồi nhập một giá thuê mới, áp dụng cho tất cả</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng và các dòng sản phẩm trong đơn bị xóa hẳn</t>
+          <t>Tất cả phòng được chọn đổi thành đúng giá mới, phòng không được chọn giữ nguyên giá cũ</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1264,10 +1268,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>A=1800000.0 B=1800000.0 untouched=3000000.0</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1285,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>DH-04</t>
+          <t>PH-08</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng</t>
+          <t>Phòng</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Xóa đơn hàng - Admin thường (phải bị chặn)</t>
+          <t>Xóa hàng loạt nhiều phòng</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1297,12 +1305,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản admin thường (không phải Super Admin) cố xóa một đơn hàng</t>
+          <t>Admin chọn nhiều phòng (một phòng chưa từng có lịch đặt, một phòng đã có lịch đặt) rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, đơn hàng vẫn còn nguyên - chỉ Super Admin mới được xóa</t>
+          <t>Phòng chưa từng có lịch đặt bị xóa hẳn; phòng đã có lịch đặt chỉ bị đóng - giống hệt quy tắc xóa từng cái một</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1312,12 +1320,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>còn tồn tại=True thông báo chặn=True</t>
+          <t>A đã xóa hẳn=True, B đã có lịch nên chỉ đóng=True</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1335,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>DH-05</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1337,7 +1345,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Khách đặt hàng qua giỏ hàng</t>
+          <t>Tạo đơn tại quầy (POS)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1347,12 +1355,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Khách thêm sản phẩm vào giỏ rồi đặt hàng (checkout)</t>
+          <t>Admin chọn món và tạo đơn ngay tại quầy bán hàng</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng mới được tạo với đúng tên/số điện thoại khách đã nhập</t>
+          <t>Đơn hàng mới được tạo, tồn kho sản phẩm bị trừ đúng số lượng</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1362,12 +1370,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4 -&gt; 5</t>
+          <t>đơn 6-&gt;7, tồn kho 49-&gt;48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1377,32 +1385,32 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>GH-01</t>
+          <t>DH-02</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Đơn hàng</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Thêm vào giỏ hàng</t>
+          <t>Cập nhật trạng thái đơn hàng</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
+          <t>Admin đổi trạng thái đơn từ "còn nợ" sang "hoàn thành"</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
+          <t>Trạng thái đơn hàng được cập nhật đúng</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1413,7 +1421,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1423,32 +1431,32 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>GH-02</t>
+          <t>DH-03</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Đơn hàng</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật số lượng trong giỏ</t>
+          <t>Xóa đơn hàng - Super Admin</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
+          <t>Tài khoản Super Admin xóa một đơn hàng test</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Số lượng trong giỏ được cập nhật đúng</t>
+          <t>Đơn hàng và các dòng sản phẩm trong đơn bị xóa hẳn</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1459,7 +1467,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1469,17 +1477,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>GH-03</t>
+          <t>DH-04</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Đơn hàng</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Xóa một món khỏi giỏ</t>
+          <t>Xóa đơn hàng - Admin thường (phải bị chặn)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1489,12 +1497,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
+          <t>Tài khoản admin thường (không phải Super Admin) cố xóa một đơn hàng</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
+          <t>Bị từ chối, đơn hàng vẫn còn nguyên - chỉ Super Admin mới được xóa</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1502,10 +1510,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>còn tồn tại=True thông báo chặn=True</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1515,32 +1527,32 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GH-04</t>
+          <t>DH-05</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Đơn hàng</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Xóa nhiều món cùng lúc</t>
+          <t>Khách đặt hàng qua giỏ hàng</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
+          <t>Khách thêm sản phẩm vào giỏ rồi đặt hàng (checkout)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
+          <t>Đơn hàng mới được tạo với đúng tên/số điện thoại khách đã nhập</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1550,12 +1562,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>gone=True kept=True</t>
+          <t>5 -&gt; 6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1577,32 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CN-01</t>
+          <t>GH-01</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán một đơn nợ</t>
+          <t>Thêm vào giỏ hàng</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
+          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đơn chuyển thành hoàn thành</t>
+          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1601,7 +1613,7 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1611,17 +1623,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CN-02</t>
+          <t>GH-02</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
+          <t>Cập nhật số lượng trong giỏ</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1631,12 +1643,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
+          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
+          <t>Số lượng trong giỏ được cập nhật đúng</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1647,7 +1659,7 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1657,32 +1669,32 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TK-01</t>
+          <t>GH-03</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Thêm tài khoản admin mới</t>
+          <t>Xóa một món khỏi giỏ</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Super Admin tạo một tài khoản admin mới</t>
+          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
+          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1690,14 +1702,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2 -&gt; 3</t>
-        </is>
-      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1707,32 +1715,32 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TK-02</t>
+          <t>GH-04</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Đổi vai trò admin</t>
+          <t>Xóa nhiều món cùng lúc</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
+          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Vai trò được cập nhật đúng</t>
+          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1740,10 +1748,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>gone=True kept=True</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1753,17 +1765,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TK-03</t>
+          <t>CN-01</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu admin</t>
+          <t>Thanh toán một đơn nợ</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1773,12 +1785,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
+          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
+          <t>Trạng thái đơn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1789,7 +1801,7 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1799,17 +1811,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TK-04</t>
+          <t>CN-02</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu khách hàng</t>
+          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1819,12 +1831,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
+          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
+          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1835,7 +1847,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1857,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TK-05</t>
+          <t>TK-01</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1855,22 +1867,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Xóa tài khoản admin</t>
+          <t>Thêm tài khoản admin mới</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
+          <t>Super Admin tạo một tài khoản admin mới</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
+          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1878,10 +1890,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2 -&gt; 3</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1907,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TK-06</t>
+          <t>TK-02</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1901,22 +1917,22 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Không cho xóa Super Admin cuối cùng</t>
+          <t>Đổi vai trò admin</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
+          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
+          <t>Vai trò được cập nhật đúng</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1924,14 +1940,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>còn tồn tại=True</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1953,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TK-07</t>
+          <t>TK-03</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,7 +1963,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Bật/tắt quyền Manager</t>
+          <t>Đặt lại mật khẩu admin</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1961,12 +1973,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
+          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -1974,14 +1986,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>promoted=True back=True</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1999,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>TK-08</t>
+          <t>TK-04</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2001,22 +2009,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký tài khoản khách hàng</t>
+          <t>Đặt lại mật khẩu khách hàng</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
+          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -2024,14 +2032,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>0 -&gt; 1</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2041,32 +2045,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>XT-01</t>
+          <t>TK-05</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin đúng mật khẩu</t>
+          <t>Xóa tài khoản admin</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
+          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công, vào được trang quản trị</t>
+          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -2077,7 +2081,7 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2087,32 +2091,32 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>XT-02</t>
+          <t>TK-06</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin sai mật khẩu</t>
+          <t>Không cho xóa Super Admin cuối cùng</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với mật khẩu sai</t>
+          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, không vào được trang quản trị</t>
+          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2122,12 +2126,12 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>HTTP 302</t>
+          <t>còn tồn tại=True</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2137,17 +2141,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>XT-03</t>
+          <t>TK-07</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Admin tự đổi mật khẩu</t>
+          <t>Bật/tắt quyền Manager</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2157,12 +2161,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
+          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
+          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2170,10 +2174,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>promoted=True back=True</t>
+        </is>
+      </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2183,32 +2191,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>XT-04</t>
+          <t>TK-08</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập khách hàng</t>
+          <t>Đăng ký tài khoản khách hàng</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
+          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2218,12 +2226,12 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>HTTP 302</t>
+          <t>0 -&gt; 1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2241,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>XT-05</t>
+          <t>XT-01</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2243,7 +2251,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất khách hàng</t>
+          <t>Đăng nhập admin đúng mật khẩu</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2253,12 +2261,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập bấm đăng xuất</t>
+          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập kết thúc</t>
+          <t>Đăng nhập thành công, vào được trang quản trị</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -2269,7 +2277,7 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2279,32 +2287,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>QR-01</t>
+          <t>XT-02</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR tuỳ ý</t>
+          <t>Đăng nhập admin sai mật khẩu</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+          <t>Đăng nhập với mật khẩu sai</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR được sinh ra thành công</t>
+          <t>Bị từ chối, không vào được trang quản trị</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2312,10 +2320,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2325,32 +2337,32 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>QR-02</t>
+          <t>XT-03</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+          <t>Admin tự đổi mật khẩu</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2361,7 +2373,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2371,32 +2383,32 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>QR-03</t>
+          <t>XT-04</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Đặt tài khoản nhận tiền mặc định</t>
+          <t>Đăng nhập khách hàng</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2411,7 +2423,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:11</t>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>
@@ -2421,47 +2433,235 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
+          <t>XT-05</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Xác thực</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Đăng xuất khách hàng</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Khách đã đăng nhập bấm đăng xuất</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Phiên đăng nhập kết thúc</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>QR-01</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Tạo mã QR tuỳ ý</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Thêm</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Ảnh mã QR được sinh ra thành công</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>QR-02</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Thêm</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>QR-03</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Đặt tài khoản nhận tiền mặc định</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>BC-01</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Báo cáo</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Xuất Excel danh sách đơn hàng</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Admin bấm xuất file Excel toàn bộ đơn hàng</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>File Excel tải về thành công, có dữ liệu bên trong</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>5405 bytes</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026 15:11</t>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>5449 bytes</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:27</t>
         </is>
       </c>
     </row>

--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>đơn 6-&gt;7, tồn kho 49-&gt;48</t>
+          <t>đơn 6-&gt;7, tồn kho 50-&gt;49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1577,32 +1577,32 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GH-01</t>
+          <t>DH-06</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Đơn hàng</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Thêm vào giỏ hàng</t>
+          <t>Đánh dấu hàng loạt "đã xong" / "còn nợ"</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
+          <t>Admin chọn nhiều đơn hàng cùng lúc rồi đánh dấu tất cả đã hoàn thành, sau đó chuyển lại thành còn nợ</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
+          <t>Tất cả đơn được chọn đổi đúng trạng thái, đơn không được chọn giữ nguyên</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1610,10 +1610,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>o1=completed o2=completed o3 (untouched)=pending</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1623,32 +1627,32 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>GH-02</t>
+          <t>DH-07</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Đơn hàng</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật số lượng trong giỏ</t>
+          <t>Xóa hàng loạt đơn hàng - Super Admin</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
+          <t>Super Admin chọn nhiều đơn hàng rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Số lượng trong giỏ được cập nhật đúng</t>
+          <t>Tất cả đơn được chọn (và các dòng sản phẩm của chúng) bị xóa hẳn</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1656,10 +1660,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>o1 gone=True o2 gone=True items gone=True</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1669,17 +1677,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GH-03</t>
+          <t>DH-08</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Đơn hàng</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Xóa một món khỏi giỏ</t>
+          <t>Xóa hàng loạt đơn hàng - Admin thường (phải bị chặn)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1689,12 +1697,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
+          <t>Tài khoản admin thường cố xóa hàng loạt đơn hàng</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
+          <t>Bị từ chối, tất cả đơn hàng vẫn còn nguyên</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1702,10 +1710,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>còn tồn tại=True</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1727,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GH-04</t>
+          <t>GH-01</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1725,22 +1737,22 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Xóa nhiều món cùng lúc</t>
+          <t>Thêm vào giỏ hàng</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
+          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
+          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1748,14 +1760,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>gone=True kept=True</t>
-        </is>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1765,17 +1773,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CN-01</t>
+          <t>GH-02</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán một đơn nợ</t>
+          <t>Cập nhật số lượng trong giỏ</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1785,12 +1793,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
+          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đơn chuyển thành hoàn thành</t>
+          <t>Số lượng trong giỏ được cập nhật đúng</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1801,7 +1809,7 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1811,32 +1819,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CN-02</t>
+          <t>GH-03</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
+          <t>Xóa một món khỏi giỏ</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
+          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
+          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1847,7 +1855,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1857,32 +1865,32 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TK-01</t>
+          <t>GH-04</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Thêm tài khoản admin mới</t>
+          <t>Xóa nhiều món cùng lúc</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Super Admin tạo một tài khoản admin mới</t>
+          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
+          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1892,12 +1900,12 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2 -&gt; 3</t>
+          <t>gone=True kept=True</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1907,17 +1915,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>TK-02</t>
+          <t>CN-01</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Đổi vai trò admin</t>
+          <t>Thanh toán một đơn nợ</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1927,12 +1935,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
+          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Vai trò được cập nhật đúng</t>
+          <t>Trạng thái đơn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1943,7 +1951,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1953,17 +1961,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TK-03</t>
+          <t>CN-02</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu admin</t>
+          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1973,12 +1981,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
+          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
+          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -1989,7 +1997,7 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2007,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>TK-04</t>
+          <t>TK-01</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2009,22 +2017,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu khách hàng</t>
+          <t>Thêm tài khoản admin mới</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
+          <t>Super Admin tạo một tài khoản admin mới</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
+          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -2032,10 +2040,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>2 -&gt; 3</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2057,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>TK-05</t>
+          <t>TK-02</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2055,22 +2067,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Xóa tài khoản admin</t>
+          <t>Đổi vai trò admin</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
+          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
+          <t>Vai trò được cập nhật đúng</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -2081,7 +2093,7 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2103,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>TK-06</t>
+          <t>TK-03</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2101,22 +2113,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Không cho xóa Super Admin cuối cùng</t>
+          <t>Đặt lại mật khẩu admin</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
+          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2124,14 +2136,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>còn tồn tại=True</t>
-        </is>
-      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2149,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TK-07</t>
+          <t>TK-04</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2151,7 +2159,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Bật/tắt quyền Manager</t>
+          <t>Đặt lại mật khẩu khách hàng</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2161,12 +2169,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
+          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2174,14 +2182,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>promoted=True back=True</t>
-        </is>
-      </c>
+      <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2195,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TK-08</t>
+          <t>TK-05</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2201,22 +2205,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký tài khoản khách hàng</t>
+          <t>Xóa tài khoản admin</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
+          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
+          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2224,14 +2228,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0 -&gt; 1</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2241,32 +2241,32 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>XT-01</t>
+          <t>TK-06</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin đúng mật khẩu</t>
+          <t>Không cho xóa Super Admin cuối cùng</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
+          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công, vào được trang quản trị</t>
+          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -2274,10 +2274,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>còn tồn tại=True</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2287,32 +2291,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>XT-02</t>
+          <t>TK-07</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin sai mật khẩu</t>
+          <t>Bật/tắt quyền Manager</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với mật khẩu sai</t>
+          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, không vào được trang quản trị</t>
+          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2322,12 +2326,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>HTTP 302</t>
+          <t>promoted=True back=True</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2337,32 +2341,32 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>XT-03</t>
+          <t>TK-08</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Admin tự đổi mật khẩu</t>
+          <t>Đăng ký tài khoản khách hàng</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
+          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
+          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2370,10 +2374,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>0 -&gt; 1</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2391,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>XT-04</t>
+          <t>XT-01</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2393,7 +2401,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập khách hàng</t>
+          <t>Đăng nhập admin đúng mật khẩu</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2403,12 +2411,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
+          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Đăng nhập thành công, vào được trang quản trị</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2416,14 +2424,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 302</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2437,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>XT-05</t>
+          <t>XT-02</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2443,7 +2447,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất khách hàng</t>
+          <t>Đăng nhập admin sai mật khẩu</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2453,12 +2457,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập bấm đăng xuất</t>
+          <t>Đăng nhập với mật khẩu sai</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập kết thúc</t>
+          <t>Bị từ chối, không vào được trang quản trị</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -2466,10 +2470,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2479,32 +2487,32 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>QR-01</t>
+          <t>XT-03</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR tuỳ ý</t>
+          <t>Admin tự đổi mật khẩu</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR được sinh ra thành công</t>
+          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2515,7 +2523,7 @@
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2525,32 +2533,32 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>QR-02</t>
+          <t>XT-04</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+          <t>Đăng nhập khách hàng</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2558,10 +2566,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2571,32 +2583,32 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>QR-03</t>
+          <t>XT-05</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Đặt tài khoản nhận tiền mặc định</t>
+          <t>Đăng xuất khách hàng</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+          <t>Khách đã đăng nhập bấm đăng xuất</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+          <t>Phiên đăng nhập kết thúc</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2604,14 +2616,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 302</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:27</t>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>
@@ -2621,47 +2629,189 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
+          <t>QR-01</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Tạo mã QR tuỳ ý</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Thêm</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Ảnh mã QR được sinh ra thành công</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>QR-02</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Thêm</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>QR-03</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Đặt tài khoản nhận tiền mặc định</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>BC-01</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Báo cáo</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Xuất Excel danh sách đơn hàng</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Admin bấm xuất file Excel toàn bộ đơn hàng</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>File Excel tải về thành công, có dữ liệu bên trong</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>5449 bytes</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026 15:27</t>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>5518 bytes</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:38</t>
         </is>
       </c>
     </row>

--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>đơn 6-&gt;7, tồn kho 50-&gt;49</t>
+          <t>đơn 6-&gt;7, tồn kho 51-&gt;50</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -1997,7 +1997,7 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Xuất Excel danh sách đơn hàng</t>
+          <t>Xuất Excel từ trang Đơn hàng</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Admin bấm xuất file Excel toàn bộ đơn hàng</t>
+          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>File Excel tải về thành công, có dữ liệu bên trong</t>
+          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2806,12 +2806,62 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>5518 bytes</t>
+          <t>all có cả 2=True, lọc nợ chỉ còn={'QA Export Debt', 'QA Bulk Order 3 (untouched)', 'Nguyễn Văn Test', 'Kiem tra dinh dang', 'Nguyễn Văn An'}</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:38</t>
+          <t>14/09/2026 15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>BC-02</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Xuất Excel từ trang Sổ nợ khách hàng</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Admin bấm "Xuất Excel" trên trang Sổ nợ khách hàng</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>File Excel tải về thành công, chỉ chứa các đơn còn nợ - không có nút "Xuất Excel" riêng ngoài sidebar nữa</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>sidebar còn mục riêng=False</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>14/09/2026 15:43</t>
         </is>
       </c>
     </row>

--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>đơn 6-&gt;7, tồn kho 51-&gt;50</t>
+          <t>đơn 6-&gt;7, tồn kho 52-&gt;51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1727,32 +1727,32 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GH-01</t>
+          <t>DM-01</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Danh mục</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Thêm vào giỏ hàng</t>
+          <t>Tab "Cơm trưa" chỉ hiện món ăn hằng ngày</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
+          <t>Khách vào tab Cơm trưa (?type=food&amp;food_kind=daily)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
+          <t>Chỉ hiện các sản phẩm admin đã đánh dấu "món ăn hằng ngày" (is_daily), không lẫn món ăn vặt</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1760,10 +1760,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>lunch có món trưa=True, lẫn món ăn vặt=False</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1773,32 +1777,32 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GH-02</t>
+          <t>DM-02</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Danh mục</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật số lượng trong giỏ</t>
+          <t>Tab "Ăn vặt" loại trừ món ăn hằng ngày</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
+          <t>Khách vào tab Ăn vặt (?type=food&amp;food_kind=snack)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Số lượng trong giỏ được cập nhật đúng</t>
+          <t>Chỉ hiện các món ăn KHÔNG được đánh dấu "món ăn hằng ngày", không lẫn cơm trưa</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1806,10 +1810,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>ăn vặt có món ăn vặt=True, lẫn cơm trưa=False</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1827,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GH-03</t>
+          <t>GH-01</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1829,22 +1837,22 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Xóa một món khỏi giỏ</t>
+          <t>Thêm vào giỏ hàng</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
+          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
+          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1855,7 +1863,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1873,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GH-04</t>
+          <t>GH-02</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1875,22 +1883,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Xóa nhiều món cùng lúc</t>
+          <t>Cập nhật số lượng trong giỏ</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
+          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
+          <t>Số lượng trong giỏ được cập nhật đúng</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1898,14 +1906,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>gone=True kept=True</t>
-        </is>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1915,32 +1919,32 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CN-01</t>
+          <t>GH-03</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán một đơn nợ</t>
+          <t>Xóa một món khỏi giỏ</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
+          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đơn chuyển thành hoàn thành</t>
+          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1951,7 +1955,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -1961,32 +1965,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CN-02</t>
+          <t>GH-04</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
+          <t>Xóa nhiều món cùng lúc</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
+          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
+          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -1994,10 +1998,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>gone=True kept=True</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2007,32 +2015,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>TK-01</t>
+          <t>CN-01</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Thêm tài khoản admin mới</t>
+          <t>Thanh toán một đơn nợ</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Super Admin tạo một tài khoản admin mới</t>
+          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
+          <t>Trạng thái đơn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -2040,14 +2048,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>2 -&gt; 3</t>
-        </is>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2057,17 +2061,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>TK-02</t>
+          <t>CN-02</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Đổi vai trò admin</t>
+          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2077,12 +2081,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
+          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Vai trò được cập nhật đúng</t>
+          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -2093,7 +2097,7 @@
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>TK-03</t>
+          <t>TK-01</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,22 +2117,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu admin</t>
+          <t>Thêm tài khoản admin mới</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
+          <t>Super Admin tạo một tài khoản admin mới</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
+          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2136,10 +2140,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>2 -&gt; 3</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2157,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TK-04</t>
+          <t>TK-02</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2159,7 +2167,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu khách hàng</t>
+          <t>Đổi vai trò admin</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2169,12 +2177,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
+          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
+          <t>Vai trò được cập nhật đúng</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2185,7 +2193,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2203,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TK-05</t>
+          <t>TK-03</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2205,22 +2213,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Xóa tài khoản admin</t>
+          <t>Đặt lại mật khẩu admin</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
+          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2231,7 +2239,7 @@
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2249,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TK-06</t>
+          <t>TK-04</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2251,22 +2259,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Không cho xóa Super Admin cuối cùng</t>
+          <t>Đặt lại mật khẩu khách hàng</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
+          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -2274,14 +2282,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>còn tồn tại=True</t>
-        </is>
-      </c>
+      <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2295,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TK-07</t>
+          <t>TK-05</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2301,22 +2305,22 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Bật/tắt quyền Manager</t>
+          <t>Xóa tài khoản admin</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
+          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
+          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2324,14 +2328,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>promoted=True back=True</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TK-08</t>
+          <t>TK-06</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2351,22 +2351,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký tài khoản khách hàng</t>
+          <t>Không cho xóa Super Admin cuối cùng</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
+          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
+          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>0 -&gt; 1</t>
+          <t>còn tồn tại=True</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2391,32 +2391,32 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>XT-01</t>
+          <t>TK-07</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin đúng mật khẩu</t>
+          <t>Bật/tắt quyền Manager</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
+          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công, vào được trang quản trị</t>
+          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2424,10 +2424,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>promoted=True back=True</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2437,32 +2441,32 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>XT-02</t>
+          <t>TK-08</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin sai mật khẩu</t>
+          <t>Đăng ký tài khoản khách hàng</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với mật khẩu sai</t>
+          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, không vào được trang quản trị</t>
+          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -2472,12 +2476,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>HTTP 302</t>
+          <t>0 -&gt; 1</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2491,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>XT-03</t>
+          <t>XT-01</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2497,22 +2501,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Admin tự đổi mật khẩu</t>
+          <t>Đăng nhập admin đúng mật khẩu</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
+          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
+          <t>Đăng nhập thành công, vào được trang quản trị</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2523,7 +2527,7 @@
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2537,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>XT-04</t>
+          <t>XT-02</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2543,7 +2547,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập khách hàng</t>
+          <t>Đăng nhập admin sai mật khẩu</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2553,12 +2557,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
+          <t>Đăng nhập với mật khẩu sai</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Bị từ chối, không vào được trang quản trị</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2573,7 +2577,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2587,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>XT-05</t>
+          <t>XT-03</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2593,22 +2597,22 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất khách hàng</t>
+          <t>Admin tự đổi mật khẩu</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập bấm đăng xuất</t>
+          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập kết thúc</t>
+          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2619,7 +2623,7 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2629,32 +2633,32 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>QR-01</t>
+          <t>XT-04</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR tuỳ ý</t>
+          <t>Đăng nhập khách hàng</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR được sinh ra thành công</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -2662,10 +2666,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2675,32 +2683,32 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>QR-02</t>
+          <t>XT-05</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+          <t>Đăng xuất khách hàng</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+          <t>Khách đã đăng nhập bấm đăng xuất</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+          <t>Phiên đăng nhập kết thúc</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -2711,7 +2719,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2729,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>QR-03</t>
+          <t>QR-01</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2731,22 +2739,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đặt tài khoản nhận tiền mặc định</t>
+          <t>Tạo mã QR tuỳ ý</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+          <t>Ảnh mã QR được sinh ra thành công</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -2754,14 +2762,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 302</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2775,32 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BC-01</t>
+          <t>QR-02</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo</t>
+          <t>QR / Thanh toán</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Xuất Excel từ trang Đơn hàng</t>
+          <t>Tạo mã QR chuyển khoản ngân hàng</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2804,14 +2808,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>all có cả 2=True, lọc nợ chỉ còn={'QA Export Debt', 'QA Bulk Order 3 (untouched)', 'Nguyễn Văn Test', 'Kiem tra dinh dang', 'Nguyễn Văn An'}</t>
-        </is>
-      </c>
+      <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>14/09/2026 15:43</t>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>
@@ -2821,47 +2821,147 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
+          <t>QR-03</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Đặt tài khoản nhận tiền mặc định</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 07:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Xuất Excel từ trang Đơn hàng</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>all có cả 2=True, lọc nợ chỉ còn={'QA Export Debt', 'Kiem tra dinh dang', 'Nguyễn Văn An', 'QA Bulk Order 3 (untouched)', 'Nguyễn Văn Test'}</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 07:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>BC-02</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Báo cáo</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Xuất Excel từ trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Admin bấm "Xuất Excel" trên trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>File Excel tải về thành công, chỉ chứa các đơn còn nợ - không có nút "Xuất Excel" riêng ngoài sidebar nữa</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>sidebar còn mục riêng=False</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>14/09/2026 15:43</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 07:52</t>
         </is>
       </c>
     </row>

--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>đơn 6-&gt;7, tồn kho 52-&gt;51</t>
+          <t>đơn 7-&gt;8, tồn kho 52-&gt;51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5 -&gt; 6</t>
+          <t>6 -&gt; 7</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CN-01</t>
+          <t>GH-05</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán một đơn nợ</t>
+          <t>Tự động điền tên/SĐT khách đã đăng nhập</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
+          <t>Khách đã đăng nhập vào trang giỏ hàng / thanh toán</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đơn chuyển thành hoàn thành</t>
+          <t>Ô tên và số điện thoại tự điền sẵn đúng thông tin đã lưu trong tài khoản, không phải gõ lại</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -2048,10 +2048,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>kiểm tra ô tên/SĐT đã điền sẵn trên trang giỏ hàng</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2061,32 +2065,32 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CN-02</t>
+          <t>GH-06</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
+          <t>Đặt hộ người khác</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
+          <t>Khách đã đăng nhập tick "Đặt hộ người khác", xóa tên tài khoản đi và gõ tên người nhận khác rồi đặt hàng</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
+          <t>Đơn hàng lưu đúng tên/SĐT người nhận vừa gõ, không lưu nhầm thành tên tài khoản đang đăng nhập</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -2094,10 +2098,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>tên lưu=Người Nhận Hộ</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2107,32 +2115,32 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>TK-01</t>
+          <t>CN-01</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Thêm tài khoản admin mới</t>
+          <t>Thanh toán một đơn nợ</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Super Admin tạo một tài khoản admin mới</t>
+          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
+          <t>Trạng thái đơn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2140,14 +2148,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>2 -&gt; 3</t>
-        </is>
-      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2157,17 +2161,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>TK-02</t>
+          <t>CN-02</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Đổi vai trò admin</t>
+          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2177,12 +2181,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
+          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Vai trò được cập nhật đúng</t>
+          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2193,7 +2197,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2207,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TK-03</t>
+          <t>TK-01</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2213,22 +2217,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu admin</t>
+          <t>Thêm tài khoản admin mới</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
+          <t>Super Admin tạo một tài khoản admin mới</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
+          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2236,10 +2240,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>2 -&gt; 3</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2257,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TK-04</t>
+          <t>TK-02</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2259,7 +2267,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu khách hàng</t>
+          <t>Đổi vai trò admin</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2269,12 +2277,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
+          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
+          <t>Vai trò được cập nhật đúng</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -2285,7 +2293,7 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2303,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TK-05</t>
+          <t>TK-03</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2305,22 +2313,22 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Xóa tài khoản admin</t>
+          <t>Đặt lại mật khẩu admin</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
+          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2331,7 +2339,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2349,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TK-06</t>
+          <t>TK-04</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2351,22 +2359,22 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Không cho xóa Super Admin cuối cùng</t>
+          <t>Đặt lại mật khẩu khách hàng</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
+          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2374,14 +2382,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>còn tồn tại=True</t>
-        </is>
-      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2395,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>TK-07</t>
+          <t>TK-05</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2401,22 +2405,22 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Bật/tắt quyền Manager</t>
+          <t>Xóa tài khoản admin</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
+          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
+          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2424,14 +2428,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>promoted=True back=True</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TK-08</t>
+          <t>TK-06</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2451,22 +2451,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký tài khoản khách hàng</t>
+          <t>Không cho xóa Super Admin cuối cùng</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
+          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
+          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0 -&gt; 1</t>
+          <t>còn tồn tại=True</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2491,32 +2491,32 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>XT-01</t>
+          <t>TK-07</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin đúng mật khẩu</t>
+          <t>Bật/tắt quyền Manager</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
+          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công, vào được trang quản trị</t>
+          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2524,10 +2524,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>promoted=True back=True</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2537,32 +2541,32 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>XT-02</t>
+          <t>TK-08</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin sai mật khẩu</t>
+          <t>Đăng ký tài khoản khách hàng</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với mật khẩu sai</t>
+          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, không vào được trang quản trị</t>
+          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2572,12 +2576,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>HTTP 302</t>
+          <t>1 -&gt; 2</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2591,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>XT-03</t>
+          <t>XT-01</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2597,22 +2601,22 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Admin tự đổi mật khẩu</t>
+          <t>Đăng nhập admin đúng mật khẩu</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
+          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
+          <t>Đăng nhập thành công, vào được trang quản trị</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2623,7 +2627,7 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2637,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>XT-04</t>
+          <t>XT-02</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2643,7 +2647,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập khách hàng</t>
+          <t>Đăng nhập admin sai mật khẩu</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2653,12 +2657,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
+          <t>Đăng nhập với mật khẩu sai</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Bị từ chối, không vào được trang quản trị</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -2673,7 +2677,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2687,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>XT-05</t>
+          <t>XT-03</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2693,22 +2697,22 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất khách hàng</t>
+          <t>Admin tự đổi mật khẩu</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập bấm đăng xuất</t>
+          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập kết thúc</t>
+          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -2719,7 +2723,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2729,32 +2733,32 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>QR-01</t>
+          <t>XT-04</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR tuỳ ý</t>
+          <t>Đăng nhập khách hàng</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR được sinh ra thành công</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -2762,10 +2766,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2783,32 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>QR-02</t>
+          <t>XT-05</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+          <t>Đăng xuất khách hàng</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+          <t>Khách đã đăng nhập bấm đăng xuất</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+          <t>Phiên đăng nhập kết thúc</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2811,7 +2819,7 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2829,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>QR-03</t>
+          <t>QR-01</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2831,22 +2839,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Đặt tài khoản nhận tiền mặc định</t>
+          <t>Tạo mã QR tuỳ ý</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+          <t>Ảnh mã QR được sinh ra thành công</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -2854,14 +2862,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 302</t>
-        </is>
-      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2871,32 +2875,32 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>BC-01</t>
+          <t>QR-02</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo</t>
+          <t>QR / Thanh toán</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Xuất Excel từ trang Đơn hàng</t>
+          <t>Tạo mã QR chuyển khoản ngân hàng</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -2904,14 +2908,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>all có cả 2=True, lọc nợ chỉ còn={'QA Export Debt', 'Kiem tra dinh dang', 'Nguyễn Văn An', 'QA Bulk Order 3 (untouched)', 'Nguyễn Văn Test'}</t>
-        </is>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 07:52</t>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>
@@ -2921,47 +2921,147 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
+          <t>QR-03</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Đặt tài khoản nhận tiền mặc định</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Xuất Excel từ trang Đơn hàng</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>all có cả 2=True, lọc nợ chỉ còn={'QA Bulk Order 3 (untouched)', 'Người Nhận Hộ', 'Nguyễn Văn An', 'QA Export Debt', 'Kiem tra dinh dang', 'Nguyễn Văn Test'}</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>BC-02</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Báo cáo</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Xuất Excel từ trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Admin bấm "Xuất Excel" trên trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>File Excel tải về thành công, chỉ chứa các đơn còn nợ - không có nút "Xuất Excel" riêng ngoài sidebar nữa</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>sidebar còn mục riêng=False</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2026 07:52</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 14:39</t>
         </is>
       </c>
     </row>

--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>đơn 7-&gt;8, tồn kho 52-&gt;51</t>
+          <t>đơn 7-&gt;8, tồn kho 53-&gt;52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Khách tự đăng ký tài khoản mới trên trang web</t>
+          <t>Khách tự đăng ký tài khoản mới trên trang web, có điền họ tên và SĐT</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng mới được tạo, đăng nhập được ngay</t>
+          <t>Tài khoản khách hàng mới được tạo với đúng họ tên và SĐT đã điền</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2591,32 +2591,32 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>XT-01</t>
+          <t>TK-09</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin đúng mật khẩu</t>
+          <t>Đăng ký thiếu tên/SĐT bị từ chối</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
+          <t>Khách cố đăng ký tài khoản nhưng bỏ trống họ tên, hoặc điền SĐT sai định dạng</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công, vào được trang quản trị</t>
+          <t>Bị từ chối với thông báo lỗi rõ ràng, không tạo tài khoản thiếu thông tin</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2624,10 +2624,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>2 -&gt; 2 (phải không đổi)</t>
+        </is>
+      </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2637,32 +2641,32 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>XT-02</t>
+          <t>TK-10</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin sai mật khẩu</t>
+          <t>Khách tự sửa thông tin cá nhân</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với mật khẩu sai</t>
+          <t>Khách đã đăng nhập vào trang "Thông tin cá nhân", đổi họ tên và SĐT rồi lưu</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, không vào được trang quản trị</t>
+          <t>Thông tin được cập nhật, tên hiển thị trên thanh điều hướng cũng đổi theo, đơn hàng sau đó tự điền theo thông tin mới</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -2672,12 +2676,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>HTTP 302</t>
+          <t>đã lưu=True, tên mới hiện ở sidebar=True, đơn hàng tự điền theo=True</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2691,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>XT-03</t>
+          <t>XT-01</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2697,22 +2701,22 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Admin tự đổi mật khẩu</t>
+          <t>Đăng nhập admin đúng mật khẩu</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
+          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
+          <t>Đăng nhập thành công, vào được trang quản trị</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -2723,7 +2727,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2737,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>XT-04</t>
+          <t>XT-02</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2743,7 +2747,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập khách hàng</t>
+          <t>Đăng nhập admin sai mật khẩu</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2753,12 +2757,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
+          <t>Đăng nhập với mật khẩu sai</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Bị từ chối, không vào được trang quản trị</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -2773,7 +2777,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>XT-05</t>
+          <t>XT-03</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2793,22 +2797,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất khách hàng</t>
+          <t>Admin tự đổi mật khẩu</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập bấm đăng xuất</t>
+          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập kết thúc</t>
+          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2819,7 +2823,7 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2829,32 +2833,32 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>QR-01</t>
+          <t>XT-04</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR tuỳ ý</t>
+          <t>Đăng nhập khách hàng</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR được sinh ra thành công</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -2862,10 +2866,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2875,32 +2883,32 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>QR-02</t>
+          <t>XT-05</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+          <t>Đăng xuất khách hàng</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+          <t>Khách đã đăng nhập bấm đăng xuất</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+          <t>Phiên đăng nhập kết thúc</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -2911,7 +2919,7 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2929,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>QR-03</t>
+          <t>QR-01</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2931,22 +2939,22 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Đặt tài khoản nhận tiền mặc định</t>
+          <t>Tạo mã QR tuỳ ý</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+          <t>Ảnh mã QR được sinh ra thành công</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -2954,14 +2962,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 302</t>
-        </is>
-      </c>
+      <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -2971,32 +2975,32 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>BC-01</t>
+          <t>QR-02</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo</t>
+          <t>QR / Thanh toán</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Xuất Excel từ trang Đơn hàng</t>
+          <t>Tạo mã QR chuyển khoản ngân hàng</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -3004,14 +3008,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>all có cả 2=True, lọc nợ chỉ còn={'QA Bulk Order 3 (untouched)', 'Người Nhận Hộ', 'Nguyễn Văn An', 'QA Export Debt', 'Kiem tra dinh dang', 'Nguyễn Văn Test'}</t>
-        </is>
-      </c>
+      <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 14:39</t>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>
@@ -3021,47 +3021,147 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
+          <t>QR-03</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Đặt tài khoản nhận tiền mặc định</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Xuất Excel từ trang Đơn hàng</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>all có cả 2=True, lọc nợ chỉ còn={'Người Nhận Hộ', 'QA Export Debt', 'QA Bulk Order 3 (untouched)', 'Nguyễn Văn Test', 'Nguyễn Văn An', 'Kiem tra dinh dang'}</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>BC-02</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Báo cáo</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Xuất Excel từ trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Admin bấm "Xuất Excel" trên trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>File Excel tải về thành công, chỉ chứa các đơn còn nợ - không có nút "Xuất Excel" riêng ngoài sidebar nữa</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>sidebar còn mục riêng=False</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2026 14:39</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 15:05</t>
         </is>
       </c>
     </row>

--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>đơn 7-&gt;8, tồn kho 53-&gt;52</t>
+          <t>đơn 7-&gt;8, tồn kho 55-&gt;54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3011,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -3106,12 +3106,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>all có cả 2=True, lọc nợ chỉ còn={'Người Nhận Hộ', 'QA Export Debt', 'QA Bulk Order 3 (untouched)', 'Nguyễn Văn Test', 'Nguyễn Văn An', 'Kiem tra dinh dang'}</t>
+          <t>all có cả 2=True, lọc nợ chỉ còn={'Người Nhận Hộ', 'QA Bulk Order 3 (untouched)', 'QA Export Debt', 'Nguyễn Văn Test', 'Nguyễn Văn An', 'Kiem tra dinh dang'}</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 15:05</t>
+          <t>15/09/2026 16:55</t>
         </is>
       </c>
     </row>

--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PH-01</t>
+          <t>SP-10</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Phòng</t>
+          <t>Sản phẩm</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Thêm phòng mới</t>
+          <t>Gắn nhãn "Đặc biệt" khi thêm/sửa sản phẩm</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Admin điền form và lưu phòng mới</t>
+          <t>Admin tick "Đặc biệt" khi thêm sản phẩm mới, rồi bỏ tick lại khi sửa sản phẩm đó</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Phòng xuất hiện trong danh sách quản lý phòng</t>
+          <t>Cờ is_special lưu đúng lúc thêm (bật) và lúc sửa (tắt); nhãn "Đặc biệt" chỉ hiện ở trang chủ và tab Cơm trưa, không hiện ở tab Ăn vặt/Đồ uống</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5 -&gt; 6</t>
+          <t>thêm bật is_special=True, nhãn hiện ở Cơm trưa=True, sửa tắt is_special=True</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PH-02</t>
+          <t>PH-01</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sửa phòng</t>
+          <t>Thêm phòng mới</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Admin đổi tên, giá, sức chứa của một phòng có sẵn</t>
+          <t>Admin điền form và lưu phòng mới</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Thông tin phòng được cập nhật đúng như đã sửa</t>
+          <t>Phòng xuất hiện trong danh sách quản lý phòng</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -1034,10 +1034,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5 -&gt; 6</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1051,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>PH-03</t>
+          <t>PH-02</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1057,7 +1061,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Bật/tắt trạng thái phòng trống</t>
+          <t>Sửa phòng</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1067,12 +1071,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Admin bấm nút đổi trạng thái mở/đóng phòng</t>
+          <t>Admin đổi tên, giá, sức chứa của một phòng có sẵn</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái available đảo ngược đúng</t>
+          <t>Thông tin phòng được cập nhật đúng như đã sửa</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -1083,7 +1087,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1097,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PH-04</t>
+          <t>PH-03</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1103,22 +1107,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Xóa phòng chưa từng có lịch đặt</t>
+          <t>Bật/tắt trạng thái phòng trống</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Admin xóa một phòng chưa từng được đặt</t>
+          <t>Admin bấm nút đổi trạng thái mở/đóng phòng</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Phòng bị xóa hẳn khỏi cơ sở dữ liệu</t>
+          <t>Trạng thái available đảo ngược đúng</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -1129,7 +1133,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1143,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PH-05</t>
+          <t>PH-04</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1149,7 +1153,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Xóa phòng đã có lịch đặt</t>
+          <t>Xóa phòng chưa từng có lịch đặt</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1159,12 +1163,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Admin xóa một phòng đã từng có người đặt (RoomBooking)</t>
+          <t>Admin xóa một phòng chưa từng được đặt</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Không xóa hẳn (vì phá vỡ lịch sử đặt phòng) - tự động đóng phòng, lịch sử vẫn giữ nguyên</t>
+          <t>Phòng bị xóa hẳn khỏi cơ sở dữ liệu</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1172,14 +1176,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>phòng vẫn còn nhưng available=False</t>
-        </is>
-      </c>
+      <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PH-06</t>
+          <t>PH-05</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật trạng thái đặt phòng</t>
+          <t>Xóa phòng đã có lịch đặt</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Admin đổi trạng thái một lượt đặt phòng (chờ/xác nhận/hủy)</t>
+          <t>Admin xóa một phòng đã từng có người đặt (RoomBooking)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đặt phòng được cập nhật đúng</t>
+          <t>Không xóa hẳn (vì phá vỡ lịch sử đặt phòng) - tự động đóng phòng, lịch sử vẫn giữ nguyên</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1222,10 +1222,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>phòng vẫn còn nhưng available=False</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1239,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PH-07</t>
+          <t>PH-06</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1245,7 +1249,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Đổi giá hàng loạt nhiều phòng</t>
+          <t>Cập nhật trạng thái đặt phòng</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1255,12 +1259,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Admin chọn nhiều phòng cùng lúc rồi nhập một giá thuê mới, áp dụng cho tất cả</t>
+          <t>Admin đổi trạng thái một lượt đặt phòng (chờ/xác nhận/hủy)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Tất cả phòng được chọn đổi thành đúng giá mới, phòng không được chọn giữ nguyên giá cũ</t>
+          <t>Trạng thái đặt phòng được cập nhật đúng</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1268,14 +1272,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>A=1800000.0 B=1800000.0 untouched=3000000.0</t>
-        </is>
-      </c>
+      <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PH-08</t>
+          <t>PH-07</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Xóa hàng loạt nhiều phòng</t>
+          <t>Đổi giá hàng loạt nhiều phòng</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Admin chọn nhiều phòng (một phòng chưa từng có lịch đặt, một phòng đã có lịch đặt) rồi xóa cùng lúc</t>
+          <t>Admin chọn nhiều phòng cùng lúc rồi nhập một giá thuê mới, áp dụng cho tất cả</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Phòng chưa từng có lịch đặt bị xóa hẳn; phòng đã có lịch đặt chỉ bị đóng - giống hệt quy tắc xóa từng cái một</t>
+          <t>Tất cả phòng được chọn đổi thành đúng giá mới, phòng không được chọn giữ nguyên giá cũ</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>A đã xóa hẳn=True, B đã có lịch nên chỉ đóng=True</t>
+          <t>A=1800000.0 B=1800000.0 untouched=3000000.0</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1335,32 +1335,32 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>PH-08</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng</t>
+          <t>Phòng</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Tạo đơn tại quầy (POS)</t>
+          <t>Xóa hàng loạt nhiều phòng</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Admin chọn món và tạo đơn ngay tại quầy bán hàng</t>
+          <t>Admin chọn nhiều phòng (một phòng chưa từng có lịch đặt, một phòng đã có lịch đặt) rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng mới được tạo, tồn kho sản phẩm bị trừ đúng số lượng</t>
+          <t>Phòng chưa từng có lịch đặt bị xóa hẳn; phòng đã có lịch đặt chỉ bị đóng - giống hệt quy tắc xóa từng cái một</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>đơn 7-&gt;8, tồn kho 55-&gt;54</t>
+          <t>A đã xóa hẳn=True, B đã có lịch nên chỉ đóng=True</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>DH-02</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1395,22 +1395,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật trạng thái đơn hàng</t>
+          <t>Tạo đơn tại quầy (POS)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Admin đổi trạng thái đơn từ "còn nợ" sang "hoàn thành"</t>
+          <t>Admin chọn món và tạo đơn ngay tại quầy bán hàng</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đơn hàng được cập nhật đúng</t>
+          <t>Đơn hàng mới được tạo, tồn kho sản phẩm bị trừ đúng số lượng</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1418,10 +1418,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>đơn 7-&gt;8, tồn kho 56-&gt;55</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1435,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>DH-03</t>
+          <t>DH-02</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1441,22 +1445,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Xóa đơn hàng - Super Admin</t>
+          <t>Cập nhật trạng thái đơn hàng</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản Super Admin xóa một đơn hàng test</t>
+          <t>Admin đổi trạng thái đơn từ "còn nợ" sang "hoàn thành"</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng và các dòng sản phẩm trong đơn bị xóa hẳn</t>
+          <t>Trạng thái đơn hàng được cập nhật đúng</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1467,7 +1471,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1481,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>DH-04</t>
+          <t>DH-03</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1487,7 +1491,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Xóa đơn hàng - Admin thường (phải bị chặn)</t>
+          <t>Xóa đơn hàng - Super Admin</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1497,12 +1501,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản admin thường (không phải Super Admin) cố xóa một đơn hàng</t>
+          <t>Tài khoản Super Admin xóa một đơn hàng test</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, đơn hàng vẫn còn nguyên - chỉ Super Admin mới được xóa</t>
+          <t>Đơn hàng và các dòng sản phẩm trong đơn bị xóa hẳn</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1510,14 +1514,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>còn tồn tại=True thông báo chặn=True</t>
-        </is>
-      </c>
+      <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>DH-05</t>
+          <t>DH-04</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1537,22 +1537,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Khách đặt hàng qua giỏ hàng</t>
+          <t>Xóa đơn hàng - Admin thường (phải bị chặn)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Khách thêm sản phẩm vào giỏ rồi đặt hàng (checkout)</t>
+          <t>Tài khoản admin thường (không phải Super Admin) cố xóa một đơn hàng</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng mới được tạo với đúng tên/số điện thoại khách đã nhập</t>
+          <t>Bị từ chối, đơn hàng vẫn còn nguyên - chỉ Super Admin mới được xóa</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6 -&gt; 7</t>
+          <t>còn tồn tại=True thông báo chặn=True</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>DH-06</t>
+          <t>DH-05</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1587,22 +1587,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Đánh dấu hàng loạt "đã xong" / "còn nợ"</t>
+          <t>Khách đặt hàng qua giỏ hàng</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Admin chọn nhiều đơn hàng cùng lúc rồi đánh dấu tất cả đã hoàn thành, sau đó chuyển lại thành còn nợ</t>
+          <t>Khách thêm sản phẩm vào giỏ rồi đặt hàng (checkout)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tất cả đơn được chọn đổi đúng trạng thái, đơn không được chọn giữ nguyên</t>
+          <t>Đơn hàng mới được tạo với đúng tên/số điện thoại khách đã nhập</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>o1=completed o2=completed o3 (untouched)=pending</t>
+          <t>6 -&gt; 7</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>DH-07</t>
+          <t>DH-06</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Xóa hàng loạt đơn hàng - Super Admin</t>
+          <t>Đánh dấu hàng loạt "đã xong" / "còn nợ"</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Super Admin chọn nhiều đơn hàng rồi xóa cùng lúc</t>
+          <t>Admin chọn nhiều đơn hàng cùng lúc rồi đánh dấu tất cả đã hoàn thành, sau đó chuyển lại thành còn nợ</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tất cả đơn được chọn (và các dòng sản phẩm của chúng) bị xóa hẳn</t>
+          <t>Tất cả đơn được chọn đổi đúng trạng thái, đơn không được chọn giữ nguyên</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>o1 gone=True o2 gone=True items gone=True</t>
+          <t>o1=completed o2=completed o3 (untouched)=pending</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>DH-08</t>
+          <t>DH-07</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Xóa hàng loạt đơn hàng - Admin thường (phải bị chặn)</t>
+          <t>Xóa hàng loạt đơn hàng - Super Admin</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản admin thường cố xóa hàng loạt đơn hàng</t>
+          <t>Super Admin chọn nhiều đơn hàng rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, tất cả đơn hàng vẫn còn nguyên</t>
+          <t>Tất cả đơn được chọn (và các dòng sản phẩm của chúng) bị xóa hẳn</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>còn tồn tại=True</t>
+          <t>o1 gone=True o2 gone=True items gone=True</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1727,32 +1727,32 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>DM-01</t>
+          <t>DH-08</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Danh mục</t>
+          <t>Đơn hàng</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Tab "Cơm trưa" chỉ hiện món ăn hằng ngày</t>
+          <t>Xóa hàng loạt đơn hàng - Admin thường (phải bị chặn)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Khách vào tab Cơm trưa (?type=food&amp;food_kind=daily)</t>
+          <t>Tài khoản admin thường cố xóa hàng loạt đơn hàng</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Chỉ hiện các sản phẩm admin đã đánh dấu "món ăn hằng ngày" (is_daily), không lẫn món ăn vặt</t>
+          <t>Bị từ chối, tất cả đơn hàng vẫn còn nguyên</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>lunch có món trưa=True, lẫn món ăn vặt=False</t>
+          <t>còn tồn tại=True</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>DM-02</t>
+          <t>DM-01</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tab "Ăn vặt" loại trừ món ăn hằng ngày</t>
+          <t>Tab "Cơm trưa" chỉ hiện món ăn hằng ngày</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Khách vào tab Ăn vặt (?type=food&amp;food_kind=snack)</t>
+          <t>Khách vào tab Cơm trưa (?type=food&amp;food_kind=daily)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Chỉ hiện các món ăn KHÔNG được đánh dấu "món ăn hằng ngày", không lẫn cơm trưa</t>
+          <t>Chỉ hiện các sản phẩm admin đã đánh dấu "món ăn hằng ngày" (is_daily), không lẫn món ăn vặt</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>ăn vặt có món ăn vặt=True, lẫn cơm trưa=False</t>
+          <t>lunch có món trưa=True, lẫn món ăn vặt=False</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1827,32 +1827,32 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GH-01</t>
+          <t>DM-02</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Danh mục</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Thêm vào giỏ hàng</t>
+          <t>Tab "Ăn vặt" loại trừ món ăn hằng ngày</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
+          <t>Khách vào tab Ăn vặt (?type=food&amp;food_kind=snack)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
+          <t>Chỉ hiện các món ăn KHÔNG được đánh dấu "món ăn hằng ngày", không lẫn cơm trưa</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1860,10 +1860,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>ăn vặt có món ăn vặt=True, lẫn cơm trưa=False</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1877,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GH-02</t>
+          <t>GH-01</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1883,22 +1887,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật số lượng trong giỏ</t>
+          <t>Thêm vào giỏ hàng</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
+          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Số lượng trong giỏ được cập nhật đúng</t>
+          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1909,7 +1913,7 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1923,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GH-03</t>
+          <t>GH-02</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1929,22 +1933,22 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Xóa một món khỏi giỏ</t>
+          <t>Cập nhật số lượng trong giỏ</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
+          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
+          <t>Số lượng trong giỏ được cập nhật đúng</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1955,7 +1959,7 @@
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1969,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GH-04</t>
+          <t>GH-03</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1975,7 +1979,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Xóa nhiều món cùng lúc</t>
+          <t>Xóa một món khỏi giỏ</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1985,12 +1989,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
+          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
+          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -1998,14 +2002,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>gone=True kept=True</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GH-05</t>
+          <t>GH-04</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2025,22 +2025,22 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tự động điền tên/SĐT khách đã đăng nhập</t>
+          <t>Xóa nhiều món cùng lúc</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập vào trang giỏ hàng / thanh toán</t>
+          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Ô tên và số điện thoại tự điền sẵn đúng thông tin đã lưu trong tài khoản, không phải gõ lại</t>
+          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>kiểm tra ô tên/SĐT đã điền sẵn trên trang giỏ hàng</t>
+          <t>gone=True kept=True</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GH-06</t>
+          <t>GH-05</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2075,22 +2075,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Đặt hộ người khác</t>
+          <t>Tự động điền tên/SĐT khách đã đăng nhập</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập tick "Đặt hộ người khác", xóa tên tài khoản đi và gõ tên người nhận khác rồi đặt hàng</t>
+          <t>Khách đã đăng nhập vào trang giỏ hàng / thanh toán</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng lưu đúng tên/SĐT người nhận vừa gõ, không lưu nhầm thành tên tài khoản đang đăng nhập</t>
+          <t>Ô tên và số điện thoại tự điền sẵn đúng thông tin đã lưu trong tài khoản, không phải gõ lại</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>tên lưu=Người Nhận Hộ</t>
+          <t>kiểm tra ô tên/SĐT đã điền sẵn trên trang giỏ hàng</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2115,32 +2115,32 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CN-01</t>
+          <t>GH-06</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán một đơn nợ</t>
+          <t>Đặt hộ người khác</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
+          <t>Khách đã đăng nhập tick "Đặt hộ người khác", xóa tên tài khoản đi và gõ tên người nhận khác rồi đặt hàng</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đơn chuyển thành hoàn thành</t>
+          <t>Đơn hàng lưu đúng tên/SĐT người nhận vừa gõ, không lưu nhầm thành tên tài khoản đang đăng nhập</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2148,10 +2148,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>tên lưu=Người Nhận Hộ</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2165,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CN-02</t>
+          <t>CN-01</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2171,7 +2175,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
+          <t>Thanh toán một đơn nợ</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2181,12 +2185,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
+          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
+          <t>Trạng thái đơn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2197,7 +2201,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2207,32 +2211,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>TK-01</t>
+          <t>CN-02</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Thêm tài khoản admin mới</t>
+          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Super Admin tạo một tài khoản admin mới</t>
+          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
+          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2240,14 +2244,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>2 -&gt; 3</t>
-        </is>
-      </c>
+      <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TK-02</t>
+          <t>TK-01</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2267,22 +2267,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Đổi vai trò admin</t>
+          <t>Thêm tài khoản admin mới</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
+          <t>Super Admin tạo một tài khoản admin mới</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Vai trò được cập nhật đúng</t>
+          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -2290,10 +2290,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>2 -&gt; 3</t>
+        </is>
+      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TK-03</t>
+          <t>TK-02</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2313,7 +2317,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu admin</t>
+          <t>Đổi vai trò admin</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2323,12 +2327,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
+          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
+          <t>Vai trò được cập nhật đúng</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2339,7 +2343,7 @@
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2353,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TK-04</t>
+          <t>TK-03</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2359,7 +2363,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu khách hàng</t>
+          <t>Đặt lại mật khẩu admin</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2369,12 +2373,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
+          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2385,7 +2389,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2399,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>TK-05</t>
+          <t>TK-04</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2405,22 +2409,22 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Xóa tài khoản admin</t>
+          <t>Đặt lại mật khẩu khách hàng</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
+          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2431,7 +2435,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2445,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TK-06</t>
+          <t>TK-05</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2451,7 +2455,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Không cho xóa Super Admin cuối cùng</t>
+          <t>Xóa tài khoản admin</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2461,12 +2465,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
+          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
+          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -2474,14 +2478,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>còn tồn tại=True</t>
-        </is>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TK-07</t>
+          <t>TK-06</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2501,22 +2501,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Bật/tắt quyền Manager</t>
+          <t>Không cho xóa Super Admin cuối cùng</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
+          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
+          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>promoted=True back=True</t>
+          <t>còn tồn tại=True</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>TK-08</t>
+          <t>TK-07</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2551,22 +2551,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký tài khoản khách hàng</t>
+          <t>Bật/tắt quyền Manager</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Khách tự đăng ký tài khoản mới trên trang web, có điền họ tên và SĐT</t>
+          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng mới được tạo với đúng họ tên và SĐT đã điền</t>
+          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1 -&gt; 2</t>
+          <t>promoted=True back=True</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>TK-09</t>
+          <t>TK-08</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thiếu tên/SĐT bị từ chối</t>
+          <t>Đăng ký tài khoản khách hàng</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Khách cố đăng ký tài khoản nhưng bỏ trống họ tên, hoặc điền SĐT sai định dạng</t>
+          <t>Khách tự đăng ký tài khoản mới trên trang web, có điền họ tên và SĐT</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối với thông báo lỗi rõ ràng, không tạo tài khoản thiếu thông tin</t>
+          <t>Tài khoản khách hàng mới được tạo với đúng họ tên và SĐT đã điền</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2 -&gt; 2 (phải không đổi)</t>
+          <t>1 -&gt; 2</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>TK-10</t>
+          <t>TK-09</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2651,22 +2651,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Khách tự sửa thông tin cá nhân</t>
+          <t>Đăng ký thiếu tên/SĐT bị từ chối</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập vào trang "Thông tin cá nhân", đổi họ tên và SĐT rồi lưu</t>
+          <t>Khách cố đăng ký tài khoản nhưng bỏ trống họ tên, hoặc điền SĐT sai định dạng</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Thông tin được cập nhật, tên hiển thị trên thanh điều hướng cũng đổi theo, đơn hàng sau đó tự điền theo thông tin mới</t>
+          <t>Bị từ chối với thông báo lỗi rõ ràng, không tạo tài khoản thiếu thông tin</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>đã lưu=True, tên mới hiện ở sidebar=True, đơn hàng tự điền theo=True</t>
+          <t>2 -&gt; 2 (phải không đổi)</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2691,32 +2691,32 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>XT-01</t>
+          <t>TK-10</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin đúng mật khẩu</t>
+          <t>Khách tự sửa thông tin cá nhân</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
+          <t>Khách đã đăng nhập vào trang "Thông tin cá nhân", đổi họ tên và SĐT rồi lưu</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công, vào được trang quản trị</t>
+          <t>Thông tin được cập nhật, tên hiển thị trên thanh điều hướng cũng đổi theo, đơn hàng sau đó tự điền theo thông tin mới</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -2724,10 +2724,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>đã lưu=True, tên mới hiện ở sidebar=True, đơn hàng tự điền theo=True</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2741,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>XT-02</t>
+          <t>XT-01</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2747,7 +2751,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin sai mật khẩu</t>
+          <t>Đăng nhập admin đúng mật khẩu</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2757,12 +2761,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với mật khẩu sai</t>
+          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, không vào được trang quản trị</t>
+          <t>Đăng nhập thành công, vào được trang quản trị</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -2770,14 +2774,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 302</t>
-        </is>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>XT-03</t>
+          <t>XT-02</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2797,22 +2797,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Admin tự đổi mật khẩu</t>
+          <t>Đăng nhập admin sai mật khẩu</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
+          <t>Đăng nhập với mật khẩu sai</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
+          <t>Bị từ chối, không vào được trang quản trị</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2820,10 +2820,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2837,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>XT-04</t>
+          <t>XT-03</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2843,22 +2847,22 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập khách hàng</t>
+          <t>Admin tự đổi mật khẩu</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
+          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -2866,14 +2870,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 302</t>
-        </is>
-      </c>
+      <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>XT-05</t>
+          <t>XT-04</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất khách hàng</t>
+          <t>Đăng nhập khách hàng</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập bấm đăng xuất</t>
+          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập kết thúc</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -2916,10 +2916,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2929,32 +2933,32 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>QR-01</t>
+          <t>XT-05</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR tuỳ ý</t>
+          <t>Đăng xuất khách hàng</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+          <t>Khách đã đăng nhập bấm đăng xuất</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR được sinh ra thành công</t>
+          <t>Phiên đăng nhập kết thúc</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -2965,7 +2969,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2979,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>QR-02</t>
+          <t>QR-01</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2985,7 +2989,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+          <t>Tạo mã QR tuỳ ý</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2995,12 +2999,12 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+          <t>Ảnh mã QR được sinh ra thành công</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -3011,7 +3015,7 @@
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3025,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>QR-03</t>
+          <t>QR-02</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3031,22 +3035,22 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Đặt tài khoản nhận tiền mặc định</t>
+          <t>Tạo mã QR chuyển khoản ngân hàng</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -3054,14 +3058,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>HTTP 302</t>
-        </is>
-      </c>
+      <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -3071,32 +3071,32 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>BC-01</t>
+          <t>QR-03</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo</t>
+          <t>QR / Thanh toán</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Xuất Excel từ trang Đơn hàng</t>
+          <t>Đặt tài khoản nhận tiền mặc định</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>all có cả 2=True, lọc nợ chỉ còn={'Người Nhận Hộ', 'QA Bulk Order 3 (untouched)', 'QA Export Debt', 'Nguyễn Văn Test', 'Nguyễn Văn An', 'Kiem tra dinh dang'}</t>
+          <t>HTTP 302</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 16:55</t>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>
@@ -3121,47 +3121,97 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Xuất Excel từ trang Đơn hàng</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>all có cả 2=True, lọc nợ chỉ còn={'Nguyễn Văn An', 'Nguyễn Văn Test', 'Kiem tra dinh dang', 'QA Bulk Order 3 (untouched)', 'Người Nhận Hộ', 'QA Export Debt'}</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>BC-02</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Báo cáo</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Xuất Excel từ trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Admin bấm "Xuất Excel" trên trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>File Excel tải về thành công, chỉ chứa các đơn còn nợ - không có nút "Xuất Excel" riêng ngoài sidebar nữa</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>sidebar còn mục riêng=False</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2026 16:55</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>15/09/2026 17:04</t>
         </is>
       </c>
     </row>

--- a/Test case/test_cases.xlsx
+++ b/Test case/test_cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>đơn 7-&gt;8, tồn kho 56-&gt;55</t>
+          <t>đơn 7-&gt;8, tồn kho 59-&gt;58</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1877,17 +1877,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GH-01</t>
+          <t>MG-01</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Thêm vào giỏ hàng</t>
+          <t>Manager đăng món mới lên "món ăn hằng ngày"</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
+          <t>Tài khoản Manager chụp/chọn ảnh, điền tên + giá rồi đăng món mới</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
+          <t>Sản phẩm mới được tạo với item_type=food, is_daily=True, ảnh được lưu vào ổ đĩa, hiện ngay trong tab Cơm trưa</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -1910,10 +1910,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>tạo đúng field=True, hiện ở Cơm trưa=True</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1923,17 +1927,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GH-02</t>
+          <t>MG-02</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Cập nhật số lượng trong giỏ</t>
+          <t>Manager tắt một món khỏi "món ăn hằng ngày"</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1943,12 +1947,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
+          <t>Manager bấm "Tắt" trên một món đang lên hôm nay</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Số lượng trong giỏ được cập nhật đúng</t>
+          <t>is_daily chuyển thành False, món biến mất khỏi tab Cơm trưa (nhưng vẫn còn ở Ăn vặt vì vẫn là food)</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -1956,10 +1960,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>is_daily=False</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -1969,32 +1977,32 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GH-03</t>
+          <t>MG-03</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Xóa một món khỏi giỏ</t>
+          <t>Manager đăng lại món đã tắt</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
+          <t>Manager bấm "Đăng lên" trên một món đang ở mục "Chưa lên món hôm nay"</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
+          <t>is_daily chuyển lại thành True, món xuất hiện lại ở tab Cơm trưa</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2002,10 +2010,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>is_daily=True</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2027,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GH-04</t>
+          <t>MG-04</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Giỏ hàng</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Xóa nhiều món cùng lúc</t>
+          <t>Khách hàng thường không vào được trang Manager</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
+          <t>Một tài khoản khách hàng thường (role=customer, không phải manager) cố truy cập /manager/daily-menu</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
+          <t>Bị từ chối với thông báo không có quyền, không thấy được form đăng món hay danh sách</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -2050,12 +2062,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>gone=True kept=True</t>
+          <t>chặn đúng=True</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2077,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GH-05</t>
+          <t>GH-01</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2075,22 +2087,22 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tự động điền tên/SĐT khách đã đăng nhập</t>
+          <t>Thêm vào giỏ hàng</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập vào trang giỏ hàng / thanh toán</t>
+          <t>Khách thêm một sản phẩm vào giỏ hàng</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Ô tên và số điện thoại tự điền sẵn đúng thông tin đã lưu trong tài khoản, không phải gõ lại</t>
+          <t>Sản phẩm xuất hiện trong giỏ với đúng số lượng</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
@@ -2098,14 +2110,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>kiểm tra ô tên/SĐT đã điền sẵn trên trang giỏ hàng</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2123,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GH-06</t>
+          <t>GH-02</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2125,22 +2133,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Đặt hộ người khác</t>
+          <t>Cập nhật số lượng trong giỏ</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập tick "Đặt hộ người khác", xóa tên tài khoản đi và gõ tên người nhận khác rồi đặt hàng</t>
+          <t>Khách đổi số lượng một sản phẩm đang có trong giỏ</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Đơn hàng lưu đúng tên/SĐT người nhận vừa gõ, không lưu nhầm thành tên tài khoản đang đăng nhập</t>
+          <t>Số lượng trong giỏ được cập nhật đúng</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2148,14 +2156,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>tên lưu=Người Nhận Hộ</t>
-        </is>
-      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2165,32 +2169,32 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CN-01</t>
+          <t>GH-03</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán một đơn nợ</t>
+          <t>Xóa một món khỏi giỏ</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
+          <t>Khách xóa một sản phẩm khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Trạng thái đơn chuyển thành hoàn thành</t>
+          <t>Sản phẩm biến mất khỏi giỏ hàng</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2201,7 +2205,7 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2211,32 +2215,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CN-02</t>
+          <t>GH-04</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Công nợ</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
+          <t>Xóa nhiều món cùng lúc</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
+          <t>Khách tick chọn nhiều sản phẩm rồi xóa cùng lúc</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
+          <t>Chỉ những sản phẩm được chọn bị xóa, các món khác vẫn còn</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2244,10 +2248,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>gone=True kept=True</t>
+        </is>
+      </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2257,32 +2265,32 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TK-01</t>
+          <t>GH-05</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Thêm tài khoản admin mới</t>
+          <t>Tự động điền tên/SĐT khách đã đăng nhập</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Super Admin tạo một tài khoản admin mới</t>
+          <t>Khách đã đăng nhập vào trang giỏ hàng / thanh toán</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
+          <t>Ô tên và số điện thoại tự điền sẵn đúng thông tin đã lưu trong tài khoản, không phải gõ lại</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -2292,12 +2300,12 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2 -&gt; 3</t>
+          <t>kiểm tra ô tên/SĐT đã điền sẵn trên trang giỏ hàng</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2307,32 +2315,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TK-02</t>
+          <t>GH-06</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Giỏ hàng</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Đổi vai trò admin</t>
+          <t>Đặt hộ người khác</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
+          <t>Khách đã đăng nhập tick "Đặt hộ người khác", xóa tên tài khoản đi và gõ tên người nhận khác rồi đặt hàng</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Vai trò được cập nhật đúng</t>
+          <t>Đơn hàng lưu đúng tên/SĐT người nhận vừa gõ, không lưu nhầm thành tên tài khoản đang đăng nhập</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2340,10 +2348,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>tên lưu=Người Nhận Hộ</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2365,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TK-03</t>
+          <t>CN-01</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu admin</t>
+          <t>Thanh toán một đơn nợ</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2373,12 +2385,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
+          <t>Super Admin xác nhận một đơn còn nợ đã được trả</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
+          <t>Trạng thái đơn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2389,7 +2401,7 @@
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2399,17 +2411,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>TK-04</t>
+          <t>CN-02</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Đặt lại mật khẩu khách hàng</t>
+          <t>Thanh toán nhiều đơn nợ cùng lúc</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2419,12 +2431,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
+          <t>Super Admin chọn nhiều đơn nợ và xác nhận trả cùng lúc</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
+          <t>Tất cả các đơn được chọn chuyển thành hoàn thành</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -2435,7 +2447,7 @@
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2457,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TK-05</t>
+          <t>TK-01</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2455,22 +2467,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Xóa tài khoản admin</t>
+          <t>Thêm tài khoản admin mới</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
+          <t>Super Admin tạo một tài khoản admin mới</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
+          <t>Tài khoản mới xuất hiện trong danh sách, đăng nhập được</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -2478,10 +2490,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>2 -&gt; 3</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2507,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TK-06</t>
+          <t>TK-02</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2501,22 +2517,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Không cho xóa Super Admin cuối cùng</t>
+          <t>Đổi vai trò admin</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Xóa</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
+          <t>Super Admin đổi vai trò một tài khoản admin thành super_admin</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
+          <t>Vai trò được cập nhật đúng</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -2524,14 +2540,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>còn tồn tại=True</t>
-        </is>
-      </c>
+      <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2553,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>TK-07</t>
+          <t>TK-03</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2551,7 +2563,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Bật/tắt quyền Manager</t>
+          <t>Đặt lại mật khẩu admin</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2561,12 +2573,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản admin khác</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
+          <t>Tài khoản đó đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -2574,14 +2586,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>promoted=True back=True</t>
-        </is>
-      </c>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2599,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>TK-08</t>
+          <t>TK-04</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2601,22 +2609,22 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký tài khoản khách hàng</t>
+          <t>Đặt lại mật khẩu khách hàng</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Khách tự đăng ký tài khoản mới trên trang web, có điền họ tên và SĐT</t>
+          <t>Super Admin đặt mật khẩu mới cho một tài khoản khách hàng</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tài khoản khách hàng mới được tạo với đúng họ tên và SĐT đã điền</t>
+          <t>Tài khoản khách hàng đăng nhập được bằng mật khẩu mới</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2624,14 +2632,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>1 -&gt; 2</t>
-        </is>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2645,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>TK-09</t>
+          <t>TK-05</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2651,22 +2655,22 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Đăng ký thiếu tên/SĐT bị từ chối</t>
+          <t>Xóa tài khoản admin</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Khách cố đăng ký tài khoản nhưng bỏ trống họ tên, hoặc điền SĐT sai định dạng</t>
+          <t>Super Admin xóa một tài khoản admin (không phải Super Admin cuối cùng)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối với thông báo lỗi rõ ràng, không tạo tài khoản thiếu thông tin</t>
+          <t>Tài khoản bị xóa hẳn, không đăng nhập được nữa</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -2674,14 +2678,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>2 -&gt; 2 (phải không đổi)</t>
-        </is>
-      </c>
+      <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>TK-10</t>
+          <t>TK-06</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Khách tự sửa thông tin cá nhân</t>
+          <t>Không cho xóa Super Admin cuối cùng</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Xóa</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập vào trang "Thông tin cá nhân", đổi họ tên và SĐT rồi lưu</t>
+          <t>Super Admin cố xóa chính Super Admin cuối cùng còn lại trong hệ thống</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Thông tin được cập nhật, tên hiển thị trên thanh điều hướng cũng đổi theo, đơn hàng sau đó tự điền theo thông tin mới</t>
+          <t>Bị từ chối, luôn còn ít nhất một Super Admin</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>đã lưu=True, tên mới hiện ở sidebar=True, đơn hàng tự điền theo=True</t>
+          <t>còn tồn tại=True</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2741,32 +2741,32 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>XT-01</t>
+          <t>TK-07</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin đúng mật khẩu</t>
+          <t>Bật/tắt quyền Manager</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
+          <t>Super Admin cấp rồi thu hồi quyền Manager cho một khách hàng</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công, vào được trang quản trị</t>
+          <t>Vai trò khách hàng đổi qua lại đúng giữa customer và manager</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -2774,10 +2774,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>promoted=True back=True</t>
+        </is>
+      </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2787,32 +2791,32 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>XT-02</t>
+          <t>TK-08</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập admin sai mật khẩu</t>
+          <t>Đăng ký tài khoản khách hàng</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập với mật khẩu sai</t>
+          <t>Khách tự đăng ký tài khoản mới trên trang web, có điền họ tên và SĐT</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Bị từ chối, không vào được trang quản trị</t>
+          <t>Tài khoản khách hàng mới được tạo với đúng họ tên và SĐT đã điền</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -2822,12 +2826,12 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>HTTP 302</t>
+          <t>3 -&gt; 4</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2837,32 +2841,32 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>XT-03</t>
+          <t>TK-09</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Admin tự đổi mật khẩu</t>
+          <t>Đăng ký thiếu tên/SĐT bị từ chối</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
+          <t>Khách cố đăng ký tài khoản nhưng bỏ trống họ tên, hoặc điền SĐT sai định dạng</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
+          <t>Bị từ chối với thông báo lỗi rõ ràng, không tạo tài khoản thiếu thông tin</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -2870,10 +2874,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>4 -&gt; 4 (phải không đổi)</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2883,32 +2891,32 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>XT-04</t>
+          <t>TK-10</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Xác thực</t>
+          <t>Tài khoản</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập khách hàng</t>
+          <t>Khách tự sửa thông tin cá nhân</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Khác</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
+          <t>Khách đã đăng nhập vào trang "Thông tin cá nhân", đổi họ tên và SĐT rồi lưu</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Đăng nhập thành công</t>
+          <t>Thông tin được cập nhật, tên hiển thị trên thanh điều hướng cũng đổi theo, đơn hàng sau đó tự điền theo thông tin mới</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -2918,12 +2926,12 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>HTTP 302</t>
+          <t>đã lưu=True, tên mới hiện ở sidebar=True, đơn hàng tự điền theo=True</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2941,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>XT-05</t>
+          <t>XT-01</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2943,7 +2951,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Đăng xuất khách hàng</t>
+          <t>Đăng nhập admin đúng mật khẩu</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2953,12 +2961,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Khách đã đăng nhập bấm đăng xuất</t>
+          <t>Đăng nhập với tài khoản/mật khẩu admin đúng</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Phiên đăng nhập kết thúc</t>
+          <t>Đăng nhập thành công, vào được trang quản trị</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -2969,7 +2977,7 @@
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -2979,32 +2987,32 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>QR-01</t>
+          <t>XT-02</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR tuỳ ý</t>
+          <t>Đăng nhập admin sai mật khẩu</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+          <t>Đăng nhập với mật khẩu sai</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR được sinh ra thành công</t>
+          <t>Bị từ chối, không vào được trang quản trị</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -3012,10 +3020,14 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -3025,32 +3037,32 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>QR-02</t>
+          <t>XT-03</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+          <t>Admin tự đổi mật khẩu</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Thêm</t>
+          <t>Sửa</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+          <t>Admin đang đăng nhập tự đổi mật khẩu của chính mình</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+          <t>Đăng nhập lại bằng mật khẩu mới thành công</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -3061,7 +3073,7 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -3071,32 +3083,32 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>QR-03</t>
+          <t>XT-04</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>QR / Thanh toán</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Đặt tài khoản nhận tiền mặc định</t>
+          <t>Đăng nhập khách hàng</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Sửa</t>
+          <t>Khác</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+          <t>Khách đăng nhập bằng tài khoản đã đăng ký</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+          <t>Đăng nhập thành công</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -3111,7 +3123,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -3121,17 +3133,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BC-01</t>
+          <t>XT-05</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Báo cáo</t>
+          <t>Xác thực</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Xuất Excel từ trang Đơn hàng</t>
+          <t>Đăng xuất khách hàng</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3141,12 +3153,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+          <t>Khách đã đăng nhập bấm đăng xuất</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+          <t>Phiên đăng nhập kết thúc</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
@@ -3154,14 +3166,10 @@
           <t>ĐẠT</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>all có cả 2=True, lọc nợ chỉ còn={'Nguyễn Văn An', 'Nguyễn Văn Test', 'Kiem tra dinh dang', 'QA Bulk Order 3 (untouched)', 'Người Nhận Hộ', 'QA Export Debt'}</t>
-        </is>
-      </c>
+      <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>15/09/2026 17:04</t>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
@@ -3171,47 +3179,239 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
+          <t>QR-01</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Tạo mã QR tuỳ ý</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Thêm</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Admin tạo một mã QR từ nội dung bất kỳ</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Ảnh mã QR được sinh ra thành công</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>QR-02</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Tạo mã QR chuyển khoản ngân hàng</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Thêm</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Admin tạo mã QR chuyển khoản với số tiền và nội dung</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Ảnh mã QR VietQR được sinh ra thành công</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>QR-03</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>QR / Thanh toán</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Đặt tài khoản nhận tiền mặc định</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Sửa</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Super Admin đặt một tài khoản ngân hàng làm tài khoản nhận tiền mặc định của quán</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Cấu hình được lưu lại, dùng cho mọi mã QR sau này</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>HTTP 302</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Xuất Excel từ trang Đơn hàng</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Khác</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Admin bấm "Xuất Excel" trên trang Đơn hàng, đúng theo bộ lọc trạng thái đang xem (tất cả/còn nợ/hoàn thành/đã hủy)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>File Excel tải về thành công, chỉ chứa đúng các đơn thuộc bộ lọc đang chọn</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>all có cả 2=True, lọc nợ chỉ còn={'Nguyễn Văn Test', 'QA Export Debt', 'Kiem tra dinh dang', 'QA Bulk Order 3 (untouched)', 'Nguyễn Văn An', 'Người Nhận Hộ'}</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026 11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>BC-02</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Báo cáo</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Xuất Excel từ trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Admin bấm "Xuất Excel" trên trang Sổ nợ khách hàng</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>File Excel tải về thành công, chỉ chứa các đơn còn nợ - không có nút "Xuất Excel" riêng ngoài sidebar nữa</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>ĐẠT</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>ĐẠT</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>sidebar còn mục riêng=False</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>15/09/2026 17:04</t>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>16/09/2026 11:15</t>
         </is>
       </c>
     </row>
